--- a/JetfWeb/JETFTAX/Download/貨件出庫批量上傳_範例.xlsx
+++ b/JetfWeb/JETFTAX/Download/貨件出庫批量上傳_範例.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Source\Jetf\JetfWeb\JETFTAX\Download\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{472B87C5-578B-48A7-B0B8-C3F8C03354E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_768980840E32B070E14EA0B970965BC841A56129" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{383CEC6D-FC70-4630-A6C8-CB46EF0EC708}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>轉出日期</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -44,6 +44,12 @@
   <si>
     <t>A8888888</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>處理狀態</t>
+  </si>
+  <si>
+    <t>已出庫</t>
   </si>
 </sst>
 </file>
@@ -119,7 +125,7 @@
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
-    <cellStyle name="一般 2" xfId="1" xr:uid="{F390750B-0C2B-4BFF-8BED-86A6A2D2D990}"/>
+    <cellStyle name="一般 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -430,7 +436,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BC5097E-EBA7-4381-AA76-5BDA81C215A8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
@@ -453,7 +459,9 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1"/>
+      <c r="D1" s="1" t="s">
+        <v>5</v>
+      </c>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -468,6 +476,9 @@
       <c r="C2" t="s">
         <v>3</v>
       </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
